--- a/docs/backlog.xlsx
+++ b/docs/backlog.xlsx
@@ -1,26 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\bupt\微处理器\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{FBA37388-778F-49F1-B2A3-50D4B99265D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5678E8A8-918D-4694-AE17-13FD6E1FC25D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Product Backlog V3" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="357" uniqueCount="234">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="397" uniqueCount="259">
   <si>
     <t>Story ID</t>
   </si>
@@ -853,13 +853,113 @@
   </si>
   <si>
     <t>Enhances administrative usability; no AI needed.</t>
+  </si>
+  <si>
+    <t>US40</t>
+  </si>
+  <si>
+    <t>US41</t>
+  </si>
+  <si>
+    <t>US42</t>
+  </si>
+  <si>
+    <t>US43</t>
+  </si>
+  <si>
+    <t>US44</t>
+  </si>
+  <si>
+    <t>Withdraw Application</t>
+  </si>
+  <si>
+    <t>As a TA applicant, I want to withdraw my application, so that I can cancel my submission if I change my decision.</t>
+  </si>
+  <si>
+    <t>1.The applicant can withdraw an application when its status is Pending or Reviewing.
+2.The applicant can withdraw an application even if it has been Accepted.
+3.Withdrawn applications are updated to "Withdrawn" status.
+4.The withdrawn application is no longer considered active.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Allows applicants to cancel submitted applications.</t>
+  </si>
+  <si>
+    <t>Cancel Job Posting</t>
+  </si>
+  <si>
+    <t>As a Module Organiser, I want to cancel a job posting, so that I can stop the recruitment process if needed.</t>
+  </si>
+  <si>
+    <t>1.The module organiser can cancel a job they created.
+2.The job status is updated to "Cancelled".
+3.Cancelled jobs are no longer visible in the applicant job list.
+4.All related applications are marked accordingly.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Supports job cancellation by organiser.</t>
+  </si>
+  <si>
+    <t>Notify Organiser on Accepted Application Withdrawal</t>
+  </si>
+  <si>
+    <t>As a Module Organiser, I want to receive a notification when an accepted applicant withdraws, so that I am aware of changes in recruitment.</t>
+  </si>
+  <si>
+    <t>1.When an Accepted application is withdrawn, a notification is generated.
+2.The notification is sent to the corresponding organiser.
+3.The notification includes applicant name and job title.
+4.The notification is stored in the system.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Triggered only for accepted applications.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Notify Applicants on Job Cancellation</t>
+  </si>
+  <si>
+    <t>As a TA applicant, I want to receive a notification when a job I applied for is cancelled, so that I know the recruitment has ended.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.When a job is cancelled, notifications are sent to all applicants of that job.
+2.Each applicant receives only one notification per job.
+3.The notification includes job title and organiser information.
+4.The notification is stored in the system.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ensures applicants are informed of job cancellation.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>View Messages</t>
+  </si>
+  <si>
+    <t>As a system user, I want to view my messages, so that I can stay informed about important updates.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.The user can view a list of messages.
+2.Each message shows sender, subject, and time.
+3.Users can only see their own messages.
+4.Messages can be marked as read.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Supports system notification viewing.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -884,6 +984,11 @@
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="8">
@@ -946,7 +1051,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -968,6 +1073,9 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1076,8 +1184,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="BacklogV3BalancedTable" displayName="BacklogV3BalancedTable" ref="A1:J45" dataDxfId="10">
-  <autoFilter ref="A1:J45" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="BacklogV3BalancedTable" displayName="BacklogV3BalancedTable" ref="A1:J50" dataDxfId="10">
+  <autoFilter ref="A1:J50" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="10">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Story ID" dataDxfId="9"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Story Name" dataDxfId="8"/>
@@ -1379,8 +1487,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J45"/>
-  <sheetFormatPr defaultRowHeight="14"/>
+  <dimension ref="A1:J50"/>
+  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="30" customWidth="1"/>
@@ -1393,7 +1501,7 @@
     <col min="9" max="10" width="15" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="24" customHeight="1">
+    <row r="1" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1425,7 +1533,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="86" customHeight="1">
+    <row r="2" spans="1:10" ht="86" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>10</v>
       </c>
@@ -1457,7 +1565,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="3" spans="1:10" ht="86" customHeight="1">
+    <row r="3" spans="1:10" ht="86" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>18</v>
       </c>
@@ -1489,7 +1597,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="4" spans="1:10" ht="86" customHeight="1">
+    <row r="4" spans="1:10" ht="86" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
         <v>23</v>
       </c>
@@ -1521,7 +1629,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="5" spans="1:10" ht="86" customHeight="1">
+    <row r="5" spans="1:10" ht="86" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
         <v>28</v>
       </c>
@@ -1553,7 +1661,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="6" spans="1:10" ht="86" customHeight="1">
+    <row r="6" spans="1:10" ht="86" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
         <v>33</v>
       </c>
@@ -1585,7 +1693,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="7" spans="1:10" ht="86" customHeight="1">
+    <row r="7" spans="1:10" ht="86" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
         <v>40</v>
       </c>
@@ -1617,7 +1725,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="8" spans="1:10" ht="86" customHeight="1">
+    <row r="8" spans="1:10" ht="86" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
         <v>47</v>
       </c>
@@ -1649,7 +1757,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="9" spans="1:10" ht="86" customHeight="1">
+    <row r="9" spans="1:10" ht="86" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
         <v>52</v>
       </c>
@@ -1681,7 +1789,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="10" spans="1:10" ht="86" customHeight="1">
+    <row r="10" spans="1:10" ht="86" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
         <v>57</v>
       </c>
@@ -1713,7 +1821,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="11" spans="1:10" ht="86" customHeight="1">
+    <row r="11" spans="1:10" ht="86" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
         <v>62</v>
       </c>
@@ -1745,7 +1853,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="12" spans="1:10" ht="86" customHeight="1">
+    <row r="12" spans="1:10" ht="86" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
         <v>67</v>
       </c>
@@ -1777,7 +1885,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="13" spans="1:10" ht="86" customHeight="1">
+    <row r="13" spans="1:10" ht="86" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
         <v>72</v>
       </c>
@@ -1809,7 +1917,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="14" spans="1:10" ht="86" customHeight="1">
+    <row r="14" spans="1:10" ht="86" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
         <v>77</v>
       </c>
@@ -1841,7 +1949,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="15" spans="1:10" ht="86" customHeight="1">
+    <row r="15" spans="1:10" ht="86" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
         <v>82</v>
       </c>
@@ -1873,7 +1981,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="16" spans="1:10" ht="86" customHeight="1">
+    <row r="16" spans="1:10" ht="86" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
         <v>87</v>
       </c>
@@ -1905,7 +2013,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="17" spans="1:10" ht="86" customHeight="1">
+    <row r="17" spans="1:10" ht="86" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
         <v>92</v>
       </c>
@@ -1937,7 +2045,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="18" spans="1:10" ht="86" customHeight="1">
+    <row r="18" spans="1:10" ht="86" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
         <v>97</v>
       </c>
@@ -1969,7 +2077,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="19" spans="1:10" ht="86" customHeight="1">
+    <row r="19" spans="1:10" ht="86" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
         <v>102</v>
       </c>
@@ -2001,7 +2109,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="20" spans="1:10" ht="86" customHeight="1">
+    <row r="20" spans="1:10" ht="86" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
         <v>107</v>
       </c>
@@ -2033,7 +2141,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="21" spans="1:10" ht="86" customHeight="1">
+    <row r="21" spans="1:10" ht="86" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="s">
         <v>112</v>
       </c>
@@ -2065,7 +2173,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="22" spans="1:10" ht="86" customHeight="1">
+    <row r="22" spans="1:10" ht="86" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
         <v>117</v>
       </c>
@@ -2079,7 +2187,7 @@
         <v>13</v>
       </c>
       <c r="E22" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F22" s="3" t="s">
         <v>120</v>
@@ -2091,13 +2199,13 @@
         <v>121</v>
       </c>
       <c r="I22" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J22" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="J22" s="2" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10" ht="86" customHeight="1">
+    </row>
+    <row r="23" spans="1:10" ht="86" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="2" t="s">
         <v>122</v>
       </c>
@@ -2129,7 +2237,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="24" spans="1:10" ht="86" customHeight="1">
+    <row r="24" spans="1:10" ht="86" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="2" t="s">
         <v>127</v>
       </c>
@@ -2161,7 +2269,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="25" spans="1:10" ht="86" customHeight="1">
+    <row r="25" spans="1:10" ht="86" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="2" t="s">
         <v>132</v>
       </c>
@@ -2193,7 +2301,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="26" spans="1:10" ht="86" customHeight="1">
+    <row r="26" spans="1:10" ht="86" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="2" t="s">
         <v>137</v>
       </c>
@@ -2207,7 +2315,7 @@
         <v>43</v>
       </c>
       <c r="E26" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F26" s="3" t="s">
         <v>140</v>
@@ -2219,13 +2327,13 @@
         <v>141</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>39</v>
+        <v>17</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="27" spans="1:10" ht="86" customHeight="1">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" ht="86" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="2" t="s">
         <v>142</v>
       </c>
@@ -2239,7 +2347,7 @@
         <v>13</v>
       </c>
       <c r="E27" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F27" s="3" t="s">
         <v>145</v>
@@ -2251,13 +2359,13 @@
         <v>146</v>
       </c>
       <c r="I27" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J27" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="J27" s="2" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="28" spans="1:10" ht="86" customHeight="1">
+    </row>
+    <row r="28" spans="1:10" ht="86" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="2" t="s">
         <v>147</v>
       </c>
@@ -2271,7 +2379,7 @@
         <v>13</v>
       </c>
       <c r="E28" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F28" s="3" t="s">
         <v>150</v>
@@ -2283,13 +2391,13 @@
         <v>151</v>
       </c>
       <c r="I28" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J28" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="J28" s="2" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="29" spans="1:10" ht="86" customHeight="1">
+    </row>
+    <row r="29" spans="1:10" ht="86" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="2" t="s">
         <v>152</v>
       </c>
@@ -2303,7 +2411,7 @@
         <v>13</v>
       </c>
       <c r="E29" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F29" s="3" t="s">
         <v>155</v>
@@ -2315,13 +2423,13 @@
         <v>156</v>
       </c>
       <c r="I29" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J29" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="J29" s="2" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="30" spans="1:10" ht="86" customHeight="1">
+    </row>
+    <row r="30" spans="1:10" ht="86" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="2" t="s">
         <v>157</v>
       </c>
@@ -2335,7 +2443,7 @@
         <v>13</v>
       </c>
       <c r="E30" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F30" s="3" t="s">
         <v>160</v>
@@ -2347,13 +2455,13 @@
         <v>161</v>
       </c>
       <c r="I30" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J30" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="J30" s="2" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="31" spans="1:10" ht="86" customHeight="1">
+    </row>
+    <row r="31" spans="1:10" ht="86" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="2" t="s">
         <v>162</v>
       </c>
@@ -2367,7 +2475,7 @@
         <v>13</v>
       </c>
       <c r="E31" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F31" s="3" t="s">
         <v>165</v>
@@ -2379,13 +2487,13 @@
         <v>166</v>
       </c>
       <c r="I31" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J31" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="J31" s="2" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="32" spans="1:10" ht="86" customHeight="1">
+    </row>
+    <row r="32" spans="1:10" ht="86" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="2" t="s">
         <v>167</v>
       </c>
@@ -2399,7 +2507,7 @@
         <v>13</v>
       </c>
       <c r="E32" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F32" s="3" t="s">
         <v>170</v>
@@ -2411,13 +2519,13 @@
         <v>171</v>
       </c>
       <c r="I32" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J32" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="J32" s="2" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="33" spans="1:10" ht="86" customHeight="1">
+    </row>
+    <row r="33" spans="1:10" ht="86" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="2" t="s">
         <v>172</v>
       </c>
@@ -2449,7 +2557,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="34" spans="1:10" ht="86" customHeight="1">
+    <row r="34" spans="1:10" ht="86" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="2" t="s">
         <v>177</v>
       </c>
@@ -2481,7 +2589,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="35" spans="1:10" ht="86" customHeight="1">
+    <row r="35" spans="1:10" ht="86" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="2" t="s">
         <v>182</v>
       </c>
@@ -2513,7 +2621,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="36" spans="1:10" ht="86" customHeight="1">
+    <row r="36" spans="1:10" ht="86" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="2" t="s">
         <v>187</v>
       </c>
@@ -2543,7 +2651,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="37" spans="1:10" ht="86" customHeight="1">
+    <row r="37" spans="1:10" ht="86" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="2" t="s">
         <v>191</v>
       </c>
@@ -2573,7 +2681,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="38" spans="1:10" ht="86" customHeight="1">
+    <row r="38" spans="1:10" ht="86" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="2" t="s">
         <v>195</v>
       </c>
@@ -2603,7 +2711,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="39" spans="1:10" ht="86" customHeight="1">
+    <row r="39" spans="1:10" ht="86" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="2" t="s">
         <v>199</v>
       </c>
@@ -2633,7 +2741,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="40" spans="1:10" ht="86" customHeight="1">
+    <row r="40" spans="1:10" ht="86" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="2" t="s">
         <v>204</v>
       </c>
@@ -2663,172 +2771,332 @@
         <v>39</v>
       </c>
     </row>
-    <row r="41" spans="1:10" ht="86" customHeight="1">
+    <row r="41" spans="1:10" ht="86" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="2" t="s">
-        <v>208</v>
+        <v>234</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>209</v>
+        <v>239</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>210</v>
-      </c>
-      <c r="D41" s="6" t="s">
-        <v>202</v>
+        <v>240</v>
+      </c>
+      <c r="D41" s="4" t="s">
+        <v>13</v>
       </c>
       <c r="E41" s="2">
-        <v>4</v>
-      </c>
-      <c r="F41" s="3" t="s">
-        <v>211</v>
+        <v>2</v>
+      </c>
+      <c r="F41" s="8" t="s">
+        <v>241</v>
       </c>
       <c r="G41" s="2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H41" s="3" t="s">
-        <v>212</v>
+        <v>242</v>
       </c>
       <c r="I41" s="2" t="s">
-        <v>39</v>
+        <v>17</v>
       </c>
       <c r="J41" s="2" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="42" spans="1:10" ht="86" customHeight="1">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10" ht="86" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="2" t="s">
-        <v>213</v>
+        <v>235</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>214</v>
+        <v>243</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>215</v>
-      </c>
-      <c r="D42" s="6" t="s">
-        <v>202</v>
+        <v>244</v>
+      </c>
+      <c r="D42" s="4" t="s">
+        <v>13</v>
       </c>
       <c r="E42" s="2">
-        <v>4</v>
-      </c>
-      <c r="F42" s="3" t="s">
-        <v>216</v>
+        <v>2</v>
+      </c>
+      <c r="F42" s="8" t="s">
+        <v>245</v>
       </c>
       <c r="G42" s="2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H42" s="3" t="s">
-        <v>217</v>
+        <v>246</v>
       </c>
       <c r="I42" s="2" t="s">
-        <v>39</v>
+        <v>17</v>
       </c>
       <c r="J42" s="2" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="43" spans="1:10" ht="86" customHeight="1">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="43" spans="1:10" ht="86" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="2" t="s">
-        <v>218</v>
+        <v>236</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>219</v>
+        <v>247</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>220</v>
-      </c>
-      <c r="D43" s="6" t="s">
-        <v>202</v>
+        <v>248</v>
+      </c>
+      <c r="D43" s="5" t="s">
+        <v>43</v>
       </c>
       <c r="E43" s="2">
-        <v>4</v>
-      </c>
-      <c r="F43" s="3" t="s">
-        <v>221</v>
+        <v>2</v>
+      </c>
+      <c r="F43" s="8" t="s">
+        <v>249</v>
       </c>
       <c r="G43" s="2">
-        <v>5</v>
-      </c>
-      <c r="H43" s="3" t="s">
-        <v>222</v>
+        <v>3</v>
+      </c>
+      <c r="H43" s="8" t="s">
+        <v>250</v>
       </c>
       <c r="I43" s="2" t="s">
-        <v>39</v>
+        <v>17</v>
       </c>
       <c r="J43" s="2" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="44" spans="1:10" ht="86" customHeight="1">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="44" spans="1:10" ht="86" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="2" t="s">
-        <v>223</v>
+        <v>237</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>224</v>
-      </c>
-      <c r="C44" s="3" t="s">
-        <v>225</v>
-      </c>
-      <c r="D44" s="7" t="s">
-        <v>226</v>
+        <v>251</v>
+      </c>
+      <c r="C44" s="8" t="s">
+        <v>252</v>
+      </c>
+      <c r="D44" s="5" t="s">
+        <v>43</v>
       </c>
       <c r="E44" s="2">
-        <v>4</v>
-      </c>
-      <c r="F44" s="3" t="s">
-        <v>227</v>
+        <v>2</v>
+      </c>
+      <c r="F44" s="8" t="s">
+        <v>253</v>
       </c>
       <c r="G44" s="2">
         <v>5</v>
       </c>
-      <c r="H44" s="3" t="s">
-        <v>228</v>
+      <c r="H44" s="8" t="s">
+        <v>254</v>
       </c>
       <c r="I44" s="2" t="s">
-        <v>39</v>
+        <v>17</v>
       </c>
       <c r="J44" s="2" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="45" spans="1:10" ht="86" customHeight="1">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="45" spans="1:10" ht="86" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="2" t="s">
-        <v>229</v>
+        <v>238</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>230</v>
-      </c>
-      <c r="C45" s="3" t="s">
-        <v>231</v>
-      </c>
-      <c r="D45" s="7" t="s">
-        <v>226</v>
+        <v>255</v>
+      </c>
+      <c r="C45" s="8" t="s">
+        <v>256</v>
+      </c>
+      <c r="D45" s="5" t="s">
+        <v>43</v>
       </c>
       <c r="E45" s="2">
-        <v>4</v>
-      </c>
-      <c r="F45" s="3" t="s">
-        <v>232</v>
+        <v>2</v>
+      </c>
+      <c r="F45" s="8" t="s">
+        <v>257</v>
       </c>
       <c r="G45" s="2">
         <v>3</v>
       </c>
-      <c r="H45" s="3" t="s">
+      <c r="H45" s="8" t="s">
+        <v>258</v>
+      </c>
+      <c r="I45" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J45" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="46" spans="1:10" ht="86" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A46" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="B46" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="C46" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="D46" s="6" t="s">
+        <v>202</v>
+      </c>
+      <c r="E46" s="2">
+        <v>4</v>
+      </c>
+      <c r="F46" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="G46" s="2">
+        <v>5</v>
+      </c>
+      <c r="H46" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="I46" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="J46" s="2" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="47" spans="1:10" ht="86" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A47" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="B47" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="C47" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="D47" s="6" t="s">
+        <v>202</v>
+      </c>
+      <c r="E47" s="2">
+        <v>4</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="G47" s="2">
+        <v>5</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="I47" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="J47" s="2" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="48" spans="1:10" ht="86" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A48" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="B48" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="C48" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="D48" s="6" t="s">
+        <v>202</v>
+      </c>
+      <c r="E48" s="2">
+        <v>4</v>
+      </c>
+      <c r="F48" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="G48" s="2">
+        <v>5</v>
+      </c>
+      <c r="H48" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="I48" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="J48" s="2" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="49" spans="1:10" ht="86" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A49" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="B49" s="3" t="s">
+        <v>224</v>
+      </c>
+      <c r="C49" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="D49" s="7" t="s">
+        <v>226</v>
+      </c>
+      <c r="E49" s="2">
+        <v>4</v>
+      </c>
+      <c r="F49" s="3" t="s">
+        <v>227</v>
+      </c>
+      <c r="G49" s="2">
+        <v>5</v>
+      </c>
+      <c r="H49" s="3" t="s">
+        <v>228</v>
+      </c>
+      <c r="I49" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="J49" s="2" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="50" spans="1:10" ht="57" x14ac:dyDescent="0.3">
+      <c r="A50" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="B50" s="3" t="s">
+        <v>230</v>
+      </c>
+      <c r="C50" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="D50" s="7" t="s">
+        <v>226</v>
+      </c>
+      <c r="E50" s="2">
+        <v>4</v>
+      </c>
+      <c r="F50" s="3" t="s">
+        <v>232</v>
+      </c>
+      <c r="G50" s="2">
+        <v>3</v>
+      </c>
+      <c r="H50" s="3" t="s">
         <v>233</v>
       </c>
-      <c r="I45" s="2" t="s">
+      <c r="I50" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="J45" s="2" t="s">
+      <c r="J50" s="2" t="s">
         <v>46</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <tableParts count="1">
-    <tablePart r:id="rId1"/>
+    <tablePart r:id="rId2"/>
   </tableParts>
 </worksheet>
 </file>